--- a/data/Archetype/archetype.xlsx
+++ b/data/Archetype/archetype.xlsx
@@ -537,14 +537,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>(list#sep=|),MaterialTag</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>int</t>
@@ -552,7 +552,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>SceneType</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>底材倾向标签(|分隔)</t>
+          <t>底材标签(枚举|分隔)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>场景锚定</t>
+          <t>场景锚定(枚举)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>weapon|sword</t>
+          <t>Weapon|Sword</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>arena</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>weapon|dagger</t>
+          <t>Weapon|Dagger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>arena</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>body_armor|helmet</t>
+          <t>BodyArmor|Helmet</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fortress</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -829,7 +829,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>weapon|staff</t>
+          <t>Weapon|Staff</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>endurance</t>
+          <t>Endurance</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -882,7 +882,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>weapon|wand</t>
+          <t>Weapon|Wand</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>swarm</t>
+          <t>Swarm</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>weapon|sword|body_armor</t>
+          <t>Weapon|Sword|BodyArmor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="K9" t="n">
